--- a/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="834">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This CH ELM concept map specifies the interpretation codes for each leading code. E.g. if positive, positive and negative or resistant-susceptible values are allowed</t>
+    <t xml:space="preserve">This CH ELM concept map specifies the interpretation codes for each leading code. E.g. if positive, positive and negative or resistant-susceptible values are allowed  </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>Salmonella sp identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>17576-0</t>
+  </si>
+  <si>
+    <t>Shigella sp identified in Specimen by Organism specific culture</t>
   </si>
   <si>
     <t>17735-2</t>
@@ -2784,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:E382"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3582,7 +3588,7 @@
         <v>38</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -3597,7 +3603,7 @@
         <v>38</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -3747,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E64" s="2"/>
     </row>
@@ -3762,7 +3768,7 @@
         <v>38</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -3807,7 +3813,7 @@
         <v>38</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -3897,7 +3903,7 @@
         <v>38</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -3912,7 +3918,7 @@
         <v>38</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -4137,7 +4143,7 @@
         <v>38</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -4152,7 +4158,7 @@
         <v>38</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -4512,7 +4518,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E115" s="2"/>
     </row>
@@ -4572,7 +4578,7 @@
         <v>38</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E119" s="2"/>
     </row>
@@ -4617,7 +4623,7 @@
         <v>38</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E122" s="2"/>
     </row>
@@ -4662,7 +4668,7 @@
         <v>38</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E125" s="2"/>
     </row>
@@ -4722,7 +4728,7 @@
         <v>38</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E129" s="2"/>
     </row>
@@ -4737,7 +4743,7 @@
         <v>38</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E130" s="2"/>
     </row>
@@ -4857,7 +4863,7 @@
         <v>38</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E138" s="2"/>
     </row>
@@ -4887,7 +4893,7 @@
         <v>38</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E140" s="2"/>
     </row>
@@ -4917,7 +4923,7 @@
         <v>38</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E142" s="2"/>
     </row>
@@ -4947,7 +4953,7 @@
         <v>38</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E144" s="2"/>
     </row>
@@ -4962,7 +4968,7 @@
         <v>38</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="E145" s="2"/>
     </row>
@@ -4977,7 +4983,7 @@
         <v>38</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E146" s="2"/>
     </row>
@@ -5037,7 +5043,7 @@
         <v>38</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E150" s="2"/>
     </row>
@@ -5052,7 +5058,7 @@
         <v>38</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E151" s="2"/>
     </row>
@@ -5202,7 +5208,7 @@
         <v>38</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E161" s="2"/>
     </row>
@@ -5217,7 +5223,7 @@
         <v>38</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E162" s="2"/>
     </row>
@@ -5262,7 +5268,7 @@
         <v>38</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E165" s="2"/>
     </row>
@@ -5277,7 +5283,7 @@
         <v>38</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E166" s="2"/>
     </row>
@@ -5427,7 +5433,7 @@
         <v>38</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E176" s="2"/>
     </row>
@@ -5442,7 +5448,7 @@
         <v>38</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E177" s="2"/>
     </row>
@@ -5577,22 +5583,22 @@
         <v>38</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>409</v>
+        <v>39</v>
       </c>
       <c r="E186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B187" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="B187" t="s" s="2">
+      <c r="C187" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D187" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D187" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="E187" s="2"/>
     </row>
@@ -5607,7 +5613,7 @@
         <v>38</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E188" s="2"/>
     </row>
@@ -5727,7 +5733,7 @@
         <v>38</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E196" s="2"/>
     </row>
@@ -5757,7 +5763,7 @@
         <v>38</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E198" s="2"/>
     </row>
@@ -5787,7 +5793,7 @@
         <v>38</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E200" s="2"/>
     </row>
@@ -5802,7 +5808,7 @@
         <v>38</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E201" s="2"/>
     </row>
@@ -5817,7 +5823,7 @@
         <v>38</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E202" s="2"/>
     </row>
@@ -5997,7 +6003,7 @@
         <v>38</v>
       </c>
       <c r="D214" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E214" s="2"/>
     </row>
@@ -6012,7 +6018,7 @@
         <v>38</v>
       </c>
       <c r="D215" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E215" s="2"/>
     </row>
@@ -6057,7 +6063,7 @@
         <v>38</v>
       </c>
       <c r="D218" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E218" s="2"/>
     </row>
@@ -6102,7 +6108,7 @@
         <v>38</v>
       </c>
       <c r="D221" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E221" s="2"/>
     </row>
@@ -6387,7 +6393,7 @@
         <v>38</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E240" s="2"/>
     </row>
@@ -6402,7 +6408,7 @@
         <v>38</v>
       </c>
       <c r="D241" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E241" s="2"/>
     </row>
@@ -6432,7 +6438,7 @@
         <v>38</v>
       </c>
       <c r="D243" t="s" s="2">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E243" s="2"/>
     </row>
@@ -6447,7 +6453,7 @@
         <v>38</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="E244" s="2"/>
     </row>
@@ -6672,7 +6678,7 @@
         <v>38</v>
       </c>
       <c r="D259" t="s" s="2">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E259" s="2"/>
     </row>
@@ -6687,7 +6693,7 @@
         <v>38</v>
       </c>
       <c r="D260" t="s" s="2">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="E260" s="2"/>
     </row>
@@ -6702,7 +6708,7 @@
         <v>38</v>
       </c>
       <c r="D261" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E261" s="2"/>
     </row>
@@ -6717,7 +6723,7 @@
         <v>38</v>
       </c>
       <c r="D262" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E262" s="2"/>
     </row>
@@ -6747,7 +6753,7 @@
         <v>38</v>
       </c>
       <c r="D264" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E264" s="2"/>
     </row>
@@ -6762,7 +6768,7 @@
         <v>38</v>
       </c>
       <c r="D265" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E265" s="2"/>
     </row>
@@ -7002,7 +7008,7 @@
         <v>38</v>
       </c>
       <c r="D281" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E281" s="2"/>
     </row>
@@ -7017,7 +7023,7 @@
         <v>38</v>
       </c>
       <c r="D282" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E282" s="2"/>
     </row>
@@ -7107,7 +7113,7 @@
         <v>38</v>
       </c>
       <c r="D288" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E288" s="2"/>
     </row>
@@ -7122,7 +7128,7 @@
         <v>38</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E289" s="2"/>
     </row>
@@ -7317,7 +7323,7 @@
         <v>38</v>
       </c>
       <c r="D302" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E302" s="2"/>
     </row>
@@ -7332,7 +7338,7 @@
         <v>38</v>
       </c>
       <c r="D303" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E303" s="2"/>
     </row>
@@ -7347,7 +7353,7 @@
         <v>38</v>
       </c>
       <c r="D304" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E304" s="2"/>
     </row>
@@ -7377,7 +7383,7 @@
         <v>38</v>
       </c>
       <c r="D306" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E306" s="2"/>
     </row>
@@ -7392,7 +7398,7 @@
         <v>38</v>
       </c>
       <c r="D307" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E307" s="2"/>
     </row>
@@ -7407,7 +7413,7 @@
         <v>38</v>
       </c>
       <c r="D308" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E308" s="2"/>
     </row>
@@ -7467,7 +7473,7 @@
         <v>38</v>
       </c>
       <c r="D312" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E312" s="2"/>
     </row>
@@ -7497,7 +7503,7 @@
         <v>38</v>
       </c>
       <c r="D314" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E314" s="2"/>
     </row>
@@ -7707,7 +7713,7 @@
         <v>38</v>
       </c>
       <c r="D328" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E328" s="2"/>
     </row>
@@ -7722,7 +7728,7 @@
         <v>38</v>
       </c>
       <c r="D329" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E329" s="2"/>
     </row>
@@ -7737,7 +7743,7 @@
         <v>38</v>
       </c>
       <c r="D330" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E330" s="2"/>
     </row>
@@ -7752,7 +7758,7 @@
         <v>38</v>
       </c>
       <c r="D331" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E331" s="2"/>
     </row>
@@ -7782,7 +7788,7 @@
         <v>38</v>
       </c>
       <c r="D333" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E333" s="2"/>
     </row>
@@ -7842,7 +7848,7 @@
         <v>38</v>
       </c>
       <c r="D337" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E337" s="2"/>
     </row>
@@ -8022,7 +8028,7 @@
         <v>38</v>
       </c>
       <c r="D349" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E349" s="2"/>
     </row>
@@ -8037,7 +8043,7 @@
         <v>38</v>
       </c>
       <c r="D350" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E350" s="2"/>
     </row>
@@ -8157,7 +8163,7 @@
         <v>38</v>
       </c>
       <c r="D358" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E358" s="2"/>
     </row>
@@ -8172,7 +8178,7 @@
         <v>38</v>
       </c>
       <c r="D359" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E359" s="2"/>
     </row>
@@ -8427,7 +8433,7 @@
         <v>38</v>
       </c>
       <c r="D376" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E376" s="2"/>
     </row>
@@ -8442,7 +8448,7 @@
         <v>38</v>
       </c>
       <c r="D377" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E377" s="2"/>
     </row>
@@ -8472,7 +8478,7 @@
         <v>38</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E379" s="2"/>
     </row>
@@ -8505,6 +8511,21 @@
         <v>39</v>
       </c>
       <c r="E381" s="2"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B382" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="C382" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D382" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E382" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -8535,7 +8556,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8552,10 +8573,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
@@ -8567,10 +8588,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
@@ -8582,10 +8603,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
@@ -8597,10 +8618,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8612,10 +8633,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
@@ -8654,7 +8675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8671,10 +8692,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
@@ -8686,10 +8707,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
@@ -8701,10 +8722,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
@@ -8716,10 +8737,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8731,10 +8752,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
@@ -8746,10 +8767,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>38</v>
@@ -8761,10 +8782,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>38</v>
@@ -8776,10 +8797,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>38</v>
@@ -8791,10 +8812,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>38</v>
@@ -8806,10 +8827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>38</v>

--- a/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1271,6 +1271,12 @@
     <t>Neisseria gonorrhoeae rRNA [Presence] in Vaginal fluid by NAA with probe detection</t>
   </si>
   <si>
+    <t>539-7</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
+  </si>
+  <si>
     <t>53917-1</t>
   </si>
   <si>
@@ -1311,12 +1317,6 @@
   </si>
   <si>
     <t>Escherichia coli shiga-like toxin identified in Specimen</t>
-  </si>
-  <si>
-    <t>539-7</t>
-  </si>
-  <si>
-    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
   </si>
   <si>
     <t>540-5</t>
@@ -5658,7 +5658,7 @@
         <v>38</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E191" s="2"/>
     </row>
@@ -5718,7 +5718,7 @@
         <v>38</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E195" s="2"/>
     </row>
@@ -5748,7 +5748,7 @@
         <v>38</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E197" s="2"/>
     </row>
@@ -5763,7 +5763,7 @@
         <v>38</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E198" s="2"/>
     </row>

--- a/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="856">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -182,6 +182,12 @@
     <t>Legionella sp DNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>101298-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Throat by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>101307-7</t>
   </si>
   <si>
@@ -314,6 +320,18 @@
     <t>Shigella species+EIEC invasion plasmid antigen H ipaH gene [Presence] in Specimen</t>
   </si>
   <si>
+    <t>105211-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchial specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>105231-5</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Sputum by NAA with probe detection</t>
+  </si>
+  <si>
     <t>105640-7</t>
   </si>
   <si>
@@ -332,6 +350,18 @@
     <t>Tick-borne encephalitis virus Ab [Interpretation] in Serum or Plasma</t>
   </si>
   <si>
+    <t>108111-6</t>
+  </si>
+  <si>
+    <t>Hantavirus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>111556-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar aspirate by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>11259-9</t>
   </si>
   <si>
@@ -926,6 +956,12 @@
     <t>Influenza virus B RNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>40988-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>41216-3</t>
   </si>
   <si>
@@ -1733,6 +1769,18 @@
     <t>Influenza virus B RNA [Presence] in Nasopharynx by NAA with probe detection</t>
   </si>
   <si>
+    <t>76088-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar lavage by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>76089-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Nasopharynx by NAA with probe detection</t>
+  </si>
+  <si>
     <t>76626-1</t>
   </si>
   <si>
@@ -1925,6 +1973,12 @@
     <t>Influenza virus B RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>85479-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>85622-9</t>
   </si>
   <si>
@@ -2117,6 +2171,12 @@
     <t>Measles virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>91133-9</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>91780-7</t>
   </si>
   <si>
@@ -2151,6 +2211,12 @@
   </si>
   <si>
     <t>Middle East respiratory syndrome coronavirus (MERS-CoV) RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>92131-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Respiratory system specimen by NAA with probe detection</t>
   </si>
   <si>
     <t>92141-1</t>
@@ -2790,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E382"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3033,22 +3099,22 @@
         <v>38</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="C17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -3078,7 +3144,7 @@
         <v>38</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -3093,7 +3159,7 @@
         <v>38</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -3108,7 +3174,7 @@
         <v>38</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -3183,7 +3249,7 @@
         <v>38</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2"/>
     </row>
@@ -3198,22 +3264,22 @@
         <v>38</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="B28" t="s" s="2">
+      <c r="C28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="E28" s="2"/>
     </row>
@@ -3228,7 +3294,7 @@
         <v>38</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29" s="2"/>
     </row>
@@ -3243,7 +3309,7 @@
         <v>38</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2"/>
     </row>
@@ -3258,7 +3324,7 @@
         <v>38</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2"/>
     </row>
@@ -3303,7 +3369,7 @@
         <v>38</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2"/>
     </row>
@@ -3333,7 +3399,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2"/>
     </row>
@@ -3348,7 +3414,7 @@
         <v>38</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2"/>
     </row>
@@ -3408,7 +3474,7 @@
         <v>38</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E41" s="2"/>
     </row>
@@ -3603,7 +3669,7 @@
         <v>38</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -3678,7 +3744,7 @@
         <v>38</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -3768,7 +3834,7 @@
         <v>38</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -3783,7 +3849,7 @@
         <v>38</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E66" s="2"/>
     </row>
@@ -3798,7 +3864,7 @@
         <v>38</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E67" s="2"/>
     </row>
@@ -3813,7 +3879,7 @@
         <v>38</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -3843,7 +3909,7 @@
         <v>38</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E70" s="2"/>
     </row>
@@ -3858,7 +3924,7 @@
         <v>38</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -3873,7 +3939,7 @@
         <v>38</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -3888,7 +3954,7 @@
         <v>38</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -3918,7 +3984,7 @@
         <v>38</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -3993,7 +4059,7 @@
         <v>38</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4158,7 +4224,7 @@
         <v>38</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -4233,7 +4299,7 @@
         <v>38</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E96" s="2"/>
     </row>
@@ -4533,7 +4599,7 @@
         <v>38</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E116" s="2"/>
     </row>
@@ -4548,7 +4614,7 @@
         <v>38</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E117" s="2"/>
     </row>
@@ -4563,7 +4629,7 @@
         <v>38</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E118" s="2"/>
     </row>
@@ -4578,7 +4644,7 @@
         <v>38</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E119" s="2"/>
     </row>
@@ -4608,7 +4674,7 @@
         <v>38</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E121" s="2"/>
     </row>
@@ -4623,7 +4689,7 @@
         <v>38</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E122" s="2"/>
     </row>
@@ -4638,7 +4704,7 @@
         <v>38</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E123" s="2"/>
     </row>
@@ -4653,7 +4719,7 @@
         <v>38</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E124" s="2"/>
     </row>
@@ -4668,7 +4734,7 @@
         <v>38</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E125" s="2"/>
     </row>
@@ -4713,7 +4779,7 @@
         <v>38</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E128" s="2"/>
     </row>
@@ -4728,7 +4794,7 @@
         <v>38</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E129" s="2"/>
     </row>
@@ -4743,7 +4809,7 @@
         <v>38</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E130" s="2"/>
     </row>
@@ -4818,7 +4884,7 @@
         <v>38</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E135" s="2"/>
     </row>
@@ -4878,7 +4944,7 @@
         <v>38</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E139" s="2"/>
     </row>
@@ -4893,7 +4959,7 @@
         <v>38</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E140" s="2"/>
     </row>
@@ -4938,7 +5004,7 @@
         <v>38</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E143" s="2"/>
     </row>
@@ -4953,7 +5019,7 @@
         <v>38</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E144" s="2"/>
     </row>
@@ -4968,7 +5034,7 @@
         <v>38</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E145" s="2"/>
     </row>
@@ -4983,7 +5049,7 @@
         <v>38</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E146" s="2"/>
     </row>
@@ -5028,7 +5094,7 @@
         <v>38</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E149" s="2"/>
     </row>
@@ -5043,7 +5109,7 @@
         <v>38</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E150" s="2"/>
     </row>
@@ -5058,7 +5124,7 @@
         <v>38</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="E151" s="2"/>
     </row>
@@ -5073,7 +5139,7 @@
         <v>38</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E152" s="2"/>
     </row>
@@ -5148,7 +5214,7 @@
         <v>38</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E157" s="2"/>
     </row>
@@ -5223,7 +5289,7 @@
         <v>38</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E162" s="2"/>
     </row>
@@ -5283,7 +5349,7 @@
         <v>38</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E166" s="2"/>
     </row>
@@ -5313,7 +5379,7 @@
         <v>38</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E168" s="2"/>
     </row>
@@ -5373,7 +5439,7 @@
         <v>38</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E172" s="2"/>
     </row>
@@ -5448,7 +5514,7 @@
         <v>38</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E177" s="2"/>
     </row>
@@ -5538,7 +5604,7 @@
         <v>38</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E183" s="2"/>
     </row>
@@ -5598,31 +5664,31 @@
         <v>38</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>411</v>
+        <v>39</v>
       </c>
       <c r="E187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B188" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="B188" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="C188" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B189" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>38</v>
@@ -5634,10 +5700,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>38</v>
@@ -5649,25 +5715,25 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="B191" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="C191" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B192" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C192" t="s" s="2">
         <v>38</v>
@@ -5679,16 +5745,16 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B193" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="B193" t="s" s="2">
+      <c r="C193" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D193" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D193" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="E193" s="2"/>
     </row>
@@ -5703,7 +5769,7 @@
         <v>38</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E194" s="2"/>
     </row>
@@ -5733,7 +5799,7 @@
         <v>38</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E196" s="2"/>
     </row>
@@ -5748,7 +5814,7 @@
         <v>38</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E197" s="2"/>
     </row>
@@ -5778,7 +5844,7 @@
         <v>38</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E199" s="2"/>
     </row>
@@ -5793,7 +5859,7 @@
         <v>38</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E200" s="2"/>
     </row>
@@ -5808,7 +5874,7 @@
         <v>38</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E201" s="2"/>
     </row>
@@ -5823,7 +5889,7 @@
         <v>38</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E202" s="2"/>
     </row>
@@ -5838,7 +5904,7 @@
         <v>38</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E203" s="2"/>
     </row>
@@ -5868,7 +5934,7 @@
         <v>38</v>
       </c>
       <c r="D205" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E205" s="2"/>
     </row>
@@ -5883,7 +5949,7 @@
         <v>38</v>
       </c>
       <c r="D206" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E206" s="2"/>
     </row>
@@ -5898,7 +5964,7 @@
         <v>38</v>
       </c>
       <c r="D207" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E207" s="2"/>
     </row>
@@ -5913,7 +5979,7 @@
         <v>38</v>
       </c>
       <c r="D208" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E208" s="2"/>
     </row>
@@ -6018,7 +6084,7 @@
         <v>38</v>
       </c>
       <c r="D215" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E215" s="2"/>
     </row>
@@ -6078,7 +6144,7 @@
         <v>38</v>
       </c>
       <c r="D219" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E219" s="2"/>
     </row>
@@ -6093,7 +6159,7 @@
         <v>38</v>
       </c>
       <c r="D220" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E220" s="2"/>
     </row>
@@ -6108,7 +6174,7 @@
         <v>38</v>
       </c>
       <c r="D221" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E221" s="2"/>
     </row>
@@ -6168,7 +6234,7 @@
         <v>38</v>
       </c>
       <c r="D225" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E225" s="2"/>
     </row>
@@ -6183,7 +6249,7 @@
         <v>38</v>
       </c>
       <c r="D226" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E226" s="2"/>
     </row>
@@ -6198,7 +6264,7 @@
         <v>38</v>
       </c>
       <c r="D227" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E227" s="2"/>
     </row>
@@ -6408,7 +6474,7 @@
         <v>38</v>
       </c>
       <c r="D241" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E241" s="2"/>
     </row>
@@ -6453,7 +6519,7 @@
         <v>38</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E244" s="2"/>
     </row>
@@ -6498,7 +6564,7 @@
         <v>38</v>
       </c>
       <c r="D247" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E247" s="2"/>
     </row>
@@ -6543,7 +6609,7 @@
         <v>38</v>
       </c>
       <c r="D250" t="s" s="2">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E250" s="2"/>
     </row>
@@ -6693,7 +6759,7 @@
         <v>38</v>
       </c>
       <c r="D260" t="s" s="2">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E260" s="2"/>
     </row>
@@ -6723,7 +6789,7 @@
         <v>38</v>
       </c>
       <c r="D262" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E262" s="2"/>
     </row>
@@ -6768,7 +6834,7 @@
         <v>38</v>
       </c>
       <c r="D265" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E265" s="2"/>
     </row>
@@ -6783,7 +6849,7 @@
         <v>38</v>
       </c>
       <c r="D266" t="s" s="2">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E266" s="2"/>
     </row>
@@ -6813,7 +6879,7 @@
         <v>38</v>
       </c>
       <c r="D268" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E268" s="2"/>
     </row>
@@ -6858,7 +6924,7 @@
         <v>38</v>
       </c>
       <c r="D271" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E271" s="2"/>
     </row>
@@ -7023,7 +7089,7 @@
         <v>38</v>
       </c>
       <c r="D282" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E282" s="2"/>
     </row>
@@ -7128,7 +7194,7 @@
         <v>38</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E289" s="2"/>
     </row>
@@ -7143,7 +7209,7 @@
         <v>38</v>
       </c>
       <c r="D290" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E290" s="2"/>
     </row>
@@ -7248,7 +7314,7 @@
         <v>38</v>
       </c>
       <c r="D297" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E297" s="2"/>
     </row>
@@ -7338,7 +7404,7 @@
         <v>38</v>
       </c>
       <c r="D303" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E303" s="2"/>
     </row>
@@ -7368,7 +7434,7 @@
         <v>38</v>
       </c>
       <c r="D305" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E305" s="2"/>
     </row>
@@ -7383,7 +7449,7 @@
         <v>38</v>
       </c>
       <c r="D306" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E306" s="2"/>
     </row>
@@ -7413,7 +7479,7 @@
         <v>38</v>
       </c>
       <c r="D308" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E308" s="2"/>
     </row>
@@ -7473,7 +7539,7 @@
         <v>38</v>
       </c>
       <c r="D312" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E312" s="2"/>
     </row>
@@ -7488,7 +7554,7 @@
         <v>38</v>
       </c>
       <c r="D313" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E313" s="2"/>
     </row>
@@ -7503,7 +7569,7 @@
         <v>38</v>
       </c>
       <c r="D314" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E314" s="2"/>
     </row>
@@ -7518,7 +7584,7 @@
         <v>38</v>
       </c>
       <c r="D315" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E315" s="2"/>
     </row>
@@ -7548,7 +7614,7 @@
         <v>38</v>
       </c>
       <c r="D317" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E317" s="2"/>
     </row>
@@ -7623,7 +7689,7 @@
         <v>38</v>
       </c>
       <c r="D322" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E322" s="2"/>
     </row>
@@ -7638,7 +7704,7 @@
         <v>38</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E323" s="2"/>
     </row>
@@ -7728,7 +7794,7 @@
         <v>38</v>
       </c>
       <c r="D329" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E329" s="2"/>
     </row>
@@ -7758,7 +7824,7 @@
         <v>38</v>
       </c>
       <c r="D331" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E331" s="2"/>
     </row>
@@ -7803,7 +7869,7 @@
         <v>38</v>
       </c>
       <c r="D334" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E334" s="2"/>
     </row>
@@ -7818,7 +7884,7 @@
         <v>38</v>
       </c>
       <c r="D335" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E335" s="2"/>
     </row>
@@ -7833,7 +7899,7 @@
         <v>38</v>
       </c>
       <c r="D336" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E336" s="2"/>
     </row>
@@ -7848,7 +7914,7 @@
         <v>38</v>
       </c>
       <c r="D337" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E337" s="2"/>
     </row>
@@ -7863,7 +7929,7 @@
         <v>38</v>
       </c>
       <c r="D338" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E338" s="2"/>
     </row>
@@ -7893,7 +7959,7 @@
         <v>38</v>
       </c>
       <c r="D340" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E340" s="2"/>
     </row>
@@ -7953,7 +8019,7 @@
         <v>38</v>
       </c>
       <c r="D344" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E344" s="2"/>
     </row>
@@ -7968,7 +8034,7 @@
         <v>38</v>
       </c>
       <c r="D345" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E345" s="2"/>
     </row>
@@ -7983,7 +8049,7 @@
         <v>38</v>
       </c>
       <c r="D346" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E346" s="2"/>
     </row>
@@ -7998,7 +8064,7 @@
         <v>38</v>
       </c>
       <c r="D347" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E347" s="2"/>
     </row>
@@ -8043,7 +8109,7 @@
         <v>38</v>
       </c>
       <c r="D350" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E350" s="2"/>
     </row>
@@ -8178,7 +8244,7 @@
         <v>38</v>
       </c>
       <c r="D359" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E359" s="2"/>
     </row>
@@ -8208,7 +8274,7 @@
         <v>38</v>
       </c>
       <c r="D361" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E361" s="2"/>
     </row>
@@ -8343,7 +8409,7 @@
         <v>38</v>
       </c>
       <c r="D370" t="s" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E370" s="2"/>
     </row>
@@ -8448,7 +8514,7 @@
         <v>38</v>
       </c>
       <c r="D377" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E377" s="2"/>
     </row>
@@ -8478,7 +8544,7 @@
         <v>38</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E379" s="2"/>
     </row>
@@ -8526,6 +8592,171 @@
         <v>39</v>
       </c>
       <c r="E382" s="2"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B383" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="C383" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D383" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E383" s="2"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="C384" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D384" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E384" s="2"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="C385" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D385" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E385" s="2"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="C386" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D386" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E386" s="2"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="C387" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D387" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E387" s="2"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="C388" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D388" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E388" s="2"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C389" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D389" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E389" s="2"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C390" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D390" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E390" s="2"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="C391" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D391" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E391" s="2"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="C392" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D392" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E392" s="2"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C393" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D393" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E393" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -8556,7 +8787,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>802</v>
+        <v>824</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8573,10 +8804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>804</v>
+        <v>826</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
@@ -8588,10 +8819,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
@@ -8603,10 +8834,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>807</v>
+        <v>829</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
@@ -8618,10 +8849,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>809</v>
+        <v>831</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8633,10 +8864,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
@@ -8675,7 +8906,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>813</v>
+        <v>835</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8692,151 +8923,151 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>817</v>
+        <v>839</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>821</v>
+        <v>843</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>824</v>
+        <v>846</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>827</v>
+        <v>849</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>829</v>
+        <v>851</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>830</v>
+        <v>852</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>831</v>
+        <v>853</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>833</v>
+        <v>855</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2"/>
     </row>

--- a/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-interpretation-code.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
